--- a/SGF_OI_LAGSGF.xlsx
+++ b/SGF_OI_LAGSGF.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\data\GITHUB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B2BC3F3C-2C07-430C-AE42-E0A793DAE9FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D20B91BD-18FF-4478-8C85-DC895752B5D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{3063807C-4DAB-4085-BEB9-C6558844D73D}"/>
   </bookViews>
@@ -105,13 +105,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -704,8 +705,8 @@
       <c r="A14" s="1">
         <v>44896</v>
       </c>
-      <c r="B14" s="2">
-        <v>5197.37</v>
+      <c r="B14" s="6">
+        <v>4432.51</v>
       </c>
       <c r="C14" s="3">
         <v>1335905.4074401341</v>
